--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104499_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104499_W5.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.02</v>
+        <v>11.3894</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5226</v>
+        <v>7.54</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4974</v>
+        <v>3.8494</v>
       </c>
       <c r="G2" t="n">
-        <v>9.918900000000001</v>
+        <v>9.9155</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2178</v>
+        <v>3.2168</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7011</v>
+        <v>6.6987</v>
       </c>
       <c r="J2" t="n">
-        <v>7.9106</v>
+        <v>7.8749</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7636</v>
+        <v>2.7439</v>
       </c>
       <c r="L2" t="n">
-        <v>5.147</v>
+        <v>5.131</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0083</v>
+        <v>2.0405</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4542</v>
+        <v>0.4729</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5541</v>
+        <v>1.5677</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6986</v>
+        <v>-0.3181</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2389</v>
+        <v>-0.1677</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4597</v>
+        <v>-0.1504</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1909</v>
+        <v>8.0116</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9171</v>
+        <v>6.1736</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2739</v>
+        <v>1.8381</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4145</v>
+        <v>5.4027</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1413</v>
+        <v>2.1425</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2732</v>
+        <v>3.2602</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9789</v>
+        <v>4.9414</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0016</v>
+        <v>1.9855</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9772</v>
+        <v>2.9559</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4356</v>
+        <v>0.4613</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0213</v>
+        <v>-0.1846</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6593</v>
+        <v>-0.3534</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.362</v>
+        <v>0.1688</v>
       </c>
       <c r="V3" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.948</v>
+        <v>6.5017</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8658</v>
+        <v>5.2128</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0823</v>
+        <v>1.2889</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6788</v>
+        <v>6.6711</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5828</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>6.0959</v>
+        <v>6.0799</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7187</v>
+        <v>5.6915</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L4" t="n">
-        <v>5.7013</v>
+        <v>5.6742</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9601</v>
+        <v>0.9796</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1844</v>
+        <v>-0.6246</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6261</v>
+        <v>-0.251</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5583</v>
+        <v>-0.3736</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9389</v>
+        <v>1.9903</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6314</v>
+        <v>1.113</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3076</v>
+        <v>0.8773</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0895</v>
+        <v>1.1065</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6725</v>
+        <v>-0.6666</v>
       </c>
       <c r="I5" t="n">
-        <v>1.762</v>
+        <v>1.7731</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4002</v>
+        <v>1.39</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3107</v>
+        <v>-0.2835</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3958</v>
+        <v>0.4286</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3388</v>
+        <v>-0.1584</v>
       </c>
       <c r="U5" t="n">
-        <v>1.057</v>
+        <v>0.587</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2806</v>
+        <v>-0.3936</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.9643</v>
+        <v>-2.9812</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6837</v>
+        <v>2.5877</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.9163</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7761</v>
+        <v>-0.368</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4127</v>
+        <v>-0.5483</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.6608</v>
+        <v>-3.2711</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1487</v>
+        <v>-1.2001</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.8096</v>
+        <v>-2.071</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0242</v>
+        <v>2.3548</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6274</v>
+        <v>0.832</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3968</v>
+        <v>1.5228</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0977</v>
+        <v>0.0188</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1693</v>
+        <v>0.1321</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0716</v>
+        <v>-0.1133</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5463</v>
+        <v>-0.7071</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9131</v>
+        <v>-4.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3668</v>
+        <v>3.4969</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9217</v>
+        <v>-0.6273</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3753</v>
+        <v>0.7864</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5464</v>
+        <v>-1.4137</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2523</v>
+        <v>-2.6823</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1917</v>
+        <v>0.1411</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0605</v>
+        <v>-2.8234</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3306</v>
+        <v>2.055</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8165</v>
+        <v>0.6452</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5141</v>
+        <v>1.4097</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1198</v>
+        <v>-0.5351</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1785</v>
+        <v>-0.3836</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2982</v>
+        <v>-0.1515</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2526</v>
+        <v>-1.2446</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9744</v>
+        <v>-0.9658</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5622</v>
+        <v>-0.5592</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,40 +1060,40 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5622</v>
+        <v>-0.5592</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3916</v>
+        <v>-2.2599</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.1355</v>
+        <v>-5.728</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7439</v>
+        <v>3.4681</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7889</v>
+        <v>-3.7935</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.8712</v>
+        <v>-4.8874</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.8404</v>
+        <v>-3.8692</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.5867</v>
+        <v>-4.6139</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0515</v>
+        <v>0.0757</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O9" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2813</v>
+        <v>-0.1509</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0948</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8135</v>
+        <v>0.4999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8948</v>
+        <v>-2.6684</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0317</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8631</v>
+        <v>-2.7549</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3316</v>
+        <v>-0.3267</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.153</v>
+        <v>-0.1495</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0893</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0584</v>
+        <v>0.1544</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>-0.0024</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0509</v>
+        <v>-2.9789</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0299</v>
+        <v>-4.6858</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9791</v>
+        <v>1.707</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5733</v>
+        <v>-3.3398</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7301</v>
+        <v>-1.3869</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3035</v>
+        <v>-1.953</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.955</v>
+        <v>-3.2127</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2162</v>
+        <v>-0.9555</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2612</v>
+        <v>-2.2572</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5283</v>
+        <v>-0.1271</v>
       </c>
       <c r="N11" t="n">
-        <v>0.486</v>
+        <v>-0.4314</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0423</v>
+        <v>0.3043</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8562</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.232</v>
+        <v>0.2519</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5383</v>
+        <v>-0.2164</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7703</v>
+        <v>0.4683</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2028</v>
+        <v>-3.1187</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6669</v>
+        <v>-5.5886</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4641</v>
+        <v>2.4699</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.332</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3808</v>
+        <v>-0.7295</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9512</v>
+        <v>1.3096</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.1862</v>
+        <v>-0.9706</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9391</v>
+        <v>-1.2313</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2471</v>
+        <v>0.2607</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1458</v>
+        <v>1.5507</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4417</v>
+        <v>0.5018</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2959</v>
+        <v>1.049</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01</v>
+        <v>0.171</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2389</v>
+        <v>-0.0653</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2489</v>
+        <v>0.2363</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.4782</v>
+        <v>14.5218</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.082700000000002</v>
+        <v>-3.340599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>17.5613</v>
+        <v>17.8626</v>
       </c>
       <c r="G13" t="n">
-        <v>14.102</v>
+        <v>14.1131</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8112</v>
+        <v>-1.795700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>15.9132</v>
+        <v>15.9088</v>
       </c>
       <c r="J13" t="n">
-        <v>6.203000000000003</v>
+        <v>5.980799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.819100000000001</v>
+        <v>-2.9375</v>
       </c>
       <c r="L13" t="n">
-        <v>9.0219</v>
+        <v>8.918200000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>7.899</v>
+        <v>8.132100000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>1.008</v>
+        <v>1.1416</v>
       </c>
       <c r="O13" t="n">
-        <v>6.891099999999999</v>
+        <v>6.991</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.99999999995449e-05</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7443</v>
+        <v>-14.796</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7441</v>
+        <v>14.796</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1019</v>
+        <v>-1.0674</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.4475</v>
+        <v>-2.3956</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3457</v>
+        <v>1.3283</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4782</v>
+        <v>1.4763</v>
       </c>
       <c r="W13" t="n">
-        <v>7.906</v>
+        <v>7.8704</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.4277</v>
+        <v>-6.3939</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6682</v>
+        <v>2.592</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3999</v>
+        <v>0.4711</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2683</v>
+        <v>2.121</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5827</v>
+        <v>1.0964</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1456</v>
+        <v>1.5509</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4371</v>
+        <v>-0.4545</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4074</v>
+        <v>0.6483</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8525</v>
+        <v>1.1926</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4451</v>
+        <v>-0.5443</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1753</v>
+        <v>0.4481</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7069</v>
+        <v>0.3583</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8822</v>
+        <v>0.0898</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7046</v>
+        <v>-0.1173</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7561</v>
+        <v>-0.4441</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9484</v>
+        <v>0.3267</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>1.405</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2754</v>
+        <v>2.2948</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6278</v>
+        <v>-0.855</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6475</v>
+        <v>3.1498</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0992</v>
+        <v>2.7661</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5497</v>
+        <v>2.5273</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4505</v>
+        <v>0.2388</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6745</v>
+        <v>2.1312</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2051</v>
+        <v>1.9822</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5306</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4247</v>
+        <v>0.6349</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3446</v>
+        <v>0.5451</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4382</v>
+        <v>0.2799</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3266</v>
+        <v>-0.1165</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1116</v>
+        <v>0.3964</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7071</v>
+        <v>0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4141</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2215</v>
+        <v>1.7362</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8334</v>
+        <v>0.7798</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0549</v>
+        <v>0.9564</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7544</v>
+        <v>-0.5821</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5251</v>
+        <v>-0.1519</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2293</v>
+        <v>-0.4302</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1407</v>
+        <v>-0.4301</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9914</v>
+        <v>-0.8693</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1493</v>
+        <v>0.4392</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6138</v>
+        <v>-0.1519</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5337</v>
+        <v>0.7174</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>-0.8694</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2156</v>
+        <v>0.7736</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1179</v>
+        <v>0.1691</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3336</v>
+        <v>0.6044</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7124</v>
+        <v>-0.6796</v>
       </c>
       <c r="E17" t="n">
-        <v>1.691</v>
+        <v>0.0186</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9786</v>
+        <v>-0.6982</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7188</v>
+        <v>-2.7121</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.909</v>
+        <v>-0.9131</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8098</v>
+        <v>-1.799</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8645</v>
+        <v>-0.881</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9391</v>
+        <v>-0.9555</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8543</v>
+        <v>-1.831</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4066</v>
+        <v>1.0113</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0506</v>
+        <v>0.4036</v>
       </c>
       <c r="U17" t="n">
-        <v>0.356</v>
+        <v>0.6077</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2328</v>
+        <v>-1.182</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0795</v>
+        <v>-1.9904</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1533</v>
+        <v>0.8084</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8244</v>
+        <v>-2.5603</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1428</v>
+        <v>-1.6231</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9672</v>
+        <v>-0.9373</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5181</v>
+        <v>-1.5161</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>-1.4931</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5354</v>
+        <v>-0.023</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3063</v>
+        <v>-1.0442</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1255</v>
+        <v>-0.13</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.9143</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5916</v>
+        <v>0.0126</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4386</v>
+        <v>-0.4743</v>
       </c>
       <c r="U18" t="n">
-        <v>0.153</v>
+        <v>0.4868</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7952</v>
+        <v>-1.46</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2702</v>
+        <v>-1.439</v>
       </c>
       <c r="F19" t="n">
-        <v>1.475</v>
+        <v>-0.021</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1255</v>
+        <v>-1.8246</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3708</v>
+        <v>0.1463</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2452</v>
+        <v>-1.9709</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8763</v>
+        <v>-1.5248</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3565</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5197000000000001</v>
+        <v>-1.542</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7507</v>
+        <v>-0.2998</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0142</v>
+        <v>0.129</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7649</v>
+        <v>-0.4289</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9488</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1207</v>
+        <v>0.3646</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3902</v>
+        <v>0.0858</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7306</v>
+        <v>0.2788</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3965</v>
+        <v>-1.6744</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6768</v>
+        <v>-1.5282</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2803</v>
+        <v>-0.1462</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5595</v>
+        <v>-0.5765</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6292</v>
+        <v>2.4537</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9303</v>
+        <v>-3.0302</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4942</v>
+        <v>-0.4102</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4861</v>
+        <v>1.7507</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0081</v>
+        <v>-2.1608</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0653</v>
+        <v>-0.1664</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1431</v>
+        <v>0.703</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9222</v>
+        <v>-0.8694</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.198</v>
+        <v>0.0128</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1825</v>
+        <v>-0.2954</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0154</v>
+        <v>0.3082</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0212</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5601</v>
+        <v>-2.6751</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0598</v>
+        <v>-3.652</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5003</v>
+        <v>0.9768</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5522</v>
+        <v>0.1333</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4706</v>
+        <v>0.376</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.0228</v>
+        <v>-0.2427</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.361</v>
+        <v>0.8616</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7796</v>
+        <v>0.348</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1406</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1912</v>
+        <v>-0.7284</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8822</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8907</v>
+        <v>1.2403</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8861</v>
+        <v>0.039</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0046</v>
+        <v>1.2013</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0246</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8549</v>
+        <v>-3.1542</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9961</v>
+        <v>-4.6656</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1412</v>
+        <v>1.5114</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9121</v>
+        <v>-2.9129</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6464</v>
+        <v>0.649</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.5585</v>
+        <v>-3.5618</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.1845</v>
+        <v>-3.2043</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1081</v>
+        <v>-3.1213</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2724</v>
+        <v>0.2914</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.009</v>
+        <v>-0.3112</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6775</v>
+        <v>-0.3232</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3315</v>
+        <v>0.0119</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3551</v>
+        <v>-3.337</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1919</v>
+        <v>-2.3893</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1632</v>
+        <v>-0.9477</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.2354</v>
+        <v>-4.2355</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4126</v>
+        <v>-1.4158</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8228</v>
+        <v>-2.8197</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3969</v>
+        <v>-2.4189</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4586</v>
+        <v>-1.4726</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8384</v>
+        <v>-1.8166</v>
       </c>
       <c r="N23" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6415</v>
+        <v>0.375</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9557</v>
+        <v>-0.1282</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3142</v>
+        <v>0.5032</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.161</v>
+        <v>-4.3579</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1722</v>
+        <v>-2.6125</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9888</v>
+        <v>-1.7453</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6961</v>
+        <v>-2.7047</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7978</v>
+        <v>-1.8034</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8983</v>
+        <v>-0.9014</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.364</v>
+        <v>-1.3879</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5452</v>
+        <v>-1.5588</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3321</v>
+        <v>-1.3168</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7597</v>
+        <v>0.0509</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8347</v>
+        <v>-0.2442</v>
       </c>
       <c r="U24" t="n">
-        <v>0.075</v>
+        <v>0.2951</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.4781</v>
+        <v>-11.8972</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.5612</v>
+        <v>-17.8625</v>
       </c>
       <c r="F25" t="n">
-        <v>4.083</v>
+        <v>5.9654</v>
       </c>
       <c r="G25" t="n">
-        <v>-14.1021</v>
+        <v>-14.1129</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8112</v>
+        <v>1.7959</v>
       </c>
       <c r="I25" t="n">
-        <v>-15.9132</v>
+        <v>-15.9089</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.8991</v>
+        <v>-8.132199999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.008</v>
+        <v>-1.1415</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.8912</v>
+        <v>-6.9907</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.2027</v>
+        <v>-5.9807</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8191</v>
+        <v>2.9373</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.022</v>
+        <v>-8.918200000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.0001000000000004053</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7444</v>
+        <v>-14.7963</v>
       </c>
       <c r="R25" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S25" t="n">
-        <v>2.102</v>
+        <v>3.6925</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3455</v>
+        <v>-1.3284</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4477</v>
+        <v>5.020499999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.478200000000001</v>
+        <v>-1.476499999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>6.427499999999999</v>
+        <v>6.3939</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.906</v>
+        <v>-7.870499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104499_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104499_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.3939</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104499_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.870499999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
